--- a/시험공부.xlsx
+++ b/시험공부.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\소프트웨어\GIT\caweb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A360CD2A-098E-434F-BED5-632EEFB00F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C10C4B6-02A7-463D-9616-F43D44FBA43E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{95918DC5-4D7A-419F-A423-84FB36FDBA28}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="41">
   <si>
     <t>컴퓨터네트워크</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -58,10 +58,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>7장 전범위 공부</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>시험</t>
   </si>
   <si>
@@ -73,106 +69,136 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>13장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14장</t>
+    <t>14장 복습</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전범위 복습</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7장 SQL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6장 - 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6장 - 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6장 복습</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7장 - 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7장 - 복습</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8장 - 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시험 공부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테이지 그리기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7장 전범위 공부
+학교 ~32페이지
+집 33~79페이지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9장 - 2 및 복습</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8장 복습</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9장 - 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>범위 내 복습</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10장 복습</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10장 - 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10장 - 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11장 - 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11장 복습</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12장 - 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12장 복습</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13장 - 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13장 - 2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>13장 복습</t>
-  </si>
-  <si>
-    <t>14장 복습</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15장 복습</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>전범위 복습</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14장 - 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14장 - 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10 ~ 12주차 과제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13 ~ 14주차 과제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>계획 변경</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>5장 SQL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>6장 SQL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7장 SQL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8장 SQL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1~5장 복습</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6장 - 2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6장 - 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6장 복습</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7장 - 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7장 - 2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7장 - 3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7장 - 복습</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8장 - 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8장 - 2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>시험 공부</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>계획 변경</t>
-  </si>
-  <si>
-    <t>스테이지 그리기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>스테이지 그리기/구현</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -182,7 +208,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-412]m&quot;월&quot;\ d&quot;일&quot;\ dddd"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -195,6 +221,24 @@
       <sz val="8"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
@@ -219,7 +263,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -352,13 +396,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -410,8 +485,26 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -774,17 +867,17 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:7" ht="59.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="12">
         <v>45985</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
-      <c r="E3" s="2" t="s">
-        <v>5</v>
+      <c r="E3" s="18" t="s">
+        <v>19</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G3" s="3"/>
     </row>
@@ -795,9 +888,6 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="G4" s="4"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.4">
@@ -807,9 +897,6 @@
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="G5" s="4"/>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.4">
@@ -817,14 +904,9 @@
         <v>45988</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>34</v>
+      <c r="E6" s="1"/>
+      <c r="F6" s="23" t="s">
+        <v>38</v>
       </c>
       <c r="G6" s="4"/>
     </row>
@@ -833,13 +915,12 @@
         <v>45989</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="E7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.4">
@@ -848,128 +929,144 @@
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="1"/>
+      <c r="F8" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="G8" s="4"/>
     </row>
     <row r="9" spans="2:7" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B9" s="11">
         <v>45991</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="6"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B10" s="12">
         <v>45992</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="1" t="s">
+      <c r="C10" s="20"/>
+      <c r="D10" s="2" t="s">
         <v>24</v>
       </c>
+      <c r="E10" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="F10" s="2"/>
-      <c r="G10" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="G10" s="3"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B11" s="10">
         <v>45993</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F11" s="1"/>
-      <c r="G11" s="4"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="19"/>
+      <c r="G11" s="4" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B12" s="10">
         <v>45994</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="4" t="s">
-        <v>17</v>
-      </c>
+      <c r="C12" s="21"/>
+      <c r="D12" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="19"/>
+      <c r="G12" s="4"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B13" s="10">
         <v>45995</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1" t="s">
+      <c r="C13" s="21"/>
+      <c r="D13" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="19"/>
+      <c r="G13" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F13" s="1"/>
-      <c r="G13" s="4"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B14" s="10">
         <v>45996</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F14" s="1"/>
-      <c r="G14" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="C14" s="21"/>
+      <c r="D14" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="19"/>
+      <c r="G14" s="4"/>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B15" s="10">
         <v>45997</v>
       </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F15" s="1"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" s="19"/>
       <c r="G15" s="4"/>
     </row>
     <row r="16" spans="2:7" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B16" s="11">
         <v>45998</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="F16" s="5"/>
-      <c r="G16" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="G16" s="6"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B17" s="10">
         <v>45999</v>
       </c>
       <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
+      <c r="D17" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="4"/>
@@ -979,12 +1076,14 @@
         <v>46000</v>
       </c>
       <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
+      <c r="D18" s="19" t="s">
+        <v>34</v>
+      </c>
       <c r="E18" s="15" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G18" s="4"/>
     </row>
@@ -993,8 +1092,8 @@
         <v>46001</v>
       </c>
       <c r="C19" s="1"/>
-      <c r="D19" s="1" t="s">
-        <v>13</v>
+      <c r="D19" s="19" t="s">
+        <v>35</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
@@ -1006,12 +1105,12 @@
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.4">
@@ -1019,10 +1118,10 @@
         <v>46003</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
@@ -1033,9 +1132,11 @@
         <v>46004</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D22" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="4"/>
@@ -1045,10 +1146,10 @@
         <v>46005</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
@@ -1059,10 +1160,10 @@
         <v>46006</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>

--- a/시험공부.xlsx
+++ b/시험공부.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\소프트웨어\GIT\caweb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C10C4B6-02A7-463D-9616-F43D44FBA43E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4780EE85-B98A-49C8-A889-17B74E3145A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{95918DC5-4D7A-419F-A423-84FB36FDBA28}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="42">
   <si>
     <t>컴퓨터네트워크</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -81,27 +81,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>6장 - 2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6장 - 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6장 복습</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7장 - 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>7장 - 복습</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8장 - 1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -119,18 +99,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>9장 - 2 및 복습</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>8장 복습</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>9장 - 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>범위 내 복습</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -199,6 +171,39 @@
   </si>
   <si>
     <t>6장 SQL</t>
+  </si>
+  <si>
+    <t>6장 복습
+7장 - 1 (6 ~ 79)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8장 - 1 ( 6 ~ 42)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9장 - 1 (6 ~ 33)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9장 - 2 (34 ~ 56)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9장 복습 및 실기 시험
+과제 공부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6장 - 1 (7 ~ 21)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6장 - 2 (21 ~ 51)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>과제</t>
   </si>
 </sst>
 </file>
@@ -433,7 +438,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -491,9 +496,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -505,6 +507,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -874,7 +882,7 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="18" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F3" s="17" t="s">
         <v>7</v>
@@ -905,8 +913,8 @@
       </c>
       <c r="C6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="23" t="s">
-        <v>38</v>
+      <c r="F6" s="22" t="s">
+        <v>31</v>
       </c>
       <c r="G6" s="4"/>
     </row>
@@ -915,12 +923,10 @@
         <v>45989</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="E7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>18</v>
-      </c>
+      <c r="E7" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="1"/>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.4">
@@ -929,90 +935,92 @@
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="2:7" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:7" ht="35.4" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B9" s="11">
         <v>45991</v>
       </c>
-      <c r="C9" s="19"/>
+      <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B10" s="12">
         <v>45992</v>
       </c>
-      <c r="C10" s="20"/>
+      <c r="C10" s="19"/>
       <c r="D10" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="G10" s="3"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B11" s="10">
         <v>45993</v>
       </c>
-      <c r="C11" s="21"/>
-      <c r="D11" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="19"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="1"/>
       <c r="G11" s="4" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B12" s="10">
         <v>45994</v>
       </c>
-      <c r="C12" s="21"/>
-      <c r="D12" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" s="19"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="1"/>
       <c r="G12" s="4"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B13" s="10">
         <v>45995</v>
       </c>
-      <c r="C13" s="21"/>
-      <c r="D13" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="F13" s="19"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="1"/>
       <c r="G13" s="4" t="s">
         <v>10</v>
       </c>
@@ -1021,40 +1029,40 @@
       <c r="B14" s="10">
         <v>45996</v>
       </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" s="19"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" s="1"/>
       <c r="G14" s="4"/>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B15" s="10">
         <v>45997</v>
       </c>
-      <c r="C15" s="21"/>
-      <c r="D15" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="F15" s="19"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15" s="1"/>
       <c r="G15" s="4"/>
     </row>
     <row r="16" spans="2:7" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B16" s="11">
         <v>45998</v>
       </c>
-      <c r="C16" s="22"/>
+      <c r="C16" s="21"/>
       <c r="D16" s="5" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="6"/>
@@ -1065,9 +1073,11 @@
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E17" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="F17" s="1"/>
       <c r="G17" s="4"/>
     </row>
@@ -1076,8 +1086,8 @@
         <v>46000</v>
       </c>
       <c r="C18" s="1"/>
-      <c r="D18" s="19" t="s">
-        <v>34</v>
+      <c r="D18" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="E18" s="15" t="s">
         <v>5</v>
@@ -1092,8 +1102,8 @@
         <v>46001</v>
       </c>
       <c r="C19" s="1"/>
-      <c r="D19" s="19" t="s">
-        <v>35</v>
+      <c r="D19" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
@@ -1118,10 +1128,10 @@
         <v>46003</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
@@ -1132,10 +1142,10 @@
         <v>46004</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
@@ -1146,7 +1156,7 @@
         <v>46005</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>9</v>

--- a/시험공부.xlsx
+++ b/시험공부.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\소프트웨어\GIT\caweb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C10C4B6-02A7-463D-9616-F43D44FBA43E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4240E53-AA60-4492-A5ED-39DE6C79AF55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{95918DC5-4D7A-419F-A423-84FB36FDBA28}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{95918DC5-4D7A-419F-A423-84FB36FDBA28}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="42">
   <si>
     <t>컴퓨터네트워크</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -106,10 +106,6 @@
   </si>
   <si>
     <t>시험 공부</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>스테이지 그리기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -199,6 +195,44 @@
   </si>
   <si>
     <t>6장 SQL</t>
+  </si>
+  <si>
+    <t>1일차
+BACK와 CONTINUE 버튼 누르면 나오는 화면 구현</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2일차
+PLAYING 화면 색상과 창 크기 고정 구현하기
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>메인화면에서 나오는 HARDEST GAME 글꼴 만들기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+스테이지 1 그림을 그리고 구현하기
+스테이지 표시하기</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -208,7 +242,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-412]m&quot;월&quot;\ d&quot;일&quot;\ dddd"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -242,6 +276,14 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -433,7 +475,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -491,9 +533,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -504,6 +543,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -841,15 +886,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C2B3A43-413E-47F0-85C4-7C095AF5A1E1}">
   <dimension ref="B1:G24"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.19921875" customWidth="1"/>
+    <col min="1" max="1" width="2.25" customWidth="1"/>
     <col min="2" max="2" width="20.5" customWidth="1"/>
-    <col min="3" max="7" width="19.09765625" customWidth="1"/>
+    <col min="3" max="5" width="19.125" customWidth="1"/>
+    <col min="6" max="6" width="55" customWidth="1"/>
+    <col min="7" max="7" width="19.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="7.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="2" spans="2:7" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:7" ht="7.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="9"/>
       <c r="C2" s="7" t="s">
         <v>0</v>
@@ -867,21 +914,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:7" ht="59.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:7" ht="59.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="12">
         <v>45985</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F3" s="17" t="s">
         <v>7</v>
       </c>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B4" s="10">
         <v>45986</v>
       </c>
@@ -890,7 +937,7 @@
       <c r="E4" s="1"/>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B5" s="10">
         <v>45987</v>
       </c>
@@ -899,71 +946,71 @@
       <c r="E5" s="1"/>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B6" s="10">
         <v>45988</v>
       </c>
       <c r="C6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="23" t="s">
-        <v>38</v>
+      <c r="F6" s="22" t="s">
+        <v>37</v>
       </c>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B7" s="10">
         <v>45989</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>18</v>
+      <c r="F7" s="22" t="s">
+        <v>40</v>
       </c>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B8" s="10">
         <v>45990</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>18</v>
+      <c r="F8" s="24" t="s">
+        <v>41</v>
       </c>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="2:7" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="11">
         <v>45991</v>
       </c>
-      <c r="C9" s="19"/>
+      <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.4">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B10" s="12">
         <v>45992</v>
       </c>
-      <c r="C10" s="20"/>
+      <c r="C10" s="19"/>
       <c r="D10" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>14</v>
@@ -971,113 +1018,113 @@
       <c r="F10" s="2"/>
       <c r="G10" s="3"/>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B11" s="10">
         <v>45993</v>
       </c>
-      <c r="C11" s="21"/>
-      <c r="D11" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="19" t="s">
+      <c r="C11" s="20"/>
+      <c r="D11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="19"/>
+      <c r="F11" s="1"/>
       <c r="G11" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.4">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B12" s="10">
         <v>45994</v>
       </c>
-      <c r="C12" s="21"/>
-      <c r="D12" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="19" t="s">
+      <c r="C12" s="20"/>
+      <c r="D12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="19"/>
+      <c r="F12" s="1"/>
       <c r="G12" s="4"/>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B13" s="10">
         <v>45995</v>
       </c>
-      <c r="C13" s="21"/>
-      <c r="D13" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="F13" s="19"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" s="1"/>
       <c r="G13" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B14" s="10">
         <v>45996</v>
       </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" s="19"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="1"/>
       <c r="G14" s="4"/>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B15" s="10">
         <v>45997</v>
       </c>
-      <c r="C15" s="21"/>
-      <c r="D15" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="F15" s="19"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="1"/>
       <c r="G15" s="4"/>
     </row>
-    <row r="16" spans="2:7" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="11">
         <v>45998</v>
       </c>
-      <c r="C16" s="22"/>
+      <c r="C16" s="21"/>
       <c r="D16" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="6"/>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B17" s="10">
         <v>45999</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="4"/>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" s="10">
         <v>46000</v>
       </c>
       <c r="C18" s="1"/>
-      <c r="D18" s="19" t="s">
-        <v>34</v>
+      <c r="D18" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="E18" s="15" t="s">
         <v>5</v>
@@ -1087,19 +1134,19 @@
       </c>
       <c r="G18" s="4"/>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="10">
         <v>46001</v>
       </c>
       <c r="C19" s="1"/>
-      <c r="D19" s="19" t="s">
-        <v>35</v>
+      <c r="D19" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="4"/>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B20" s="10">
         <v>46002</v>
       </c>
@@ -1113,7 +1160,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21" s="10">
         <v>46003</v>
       </c>
@@ -1121,13 +1168,13 @@
         <v>17</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="4"/>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B22" s="10">
         <v>46004</v>
       </c>
@@ -1135,13 +1182,13 @@
         <v>17</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="4"/>
     </row>
-    <row r="23" spans="2:7" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="10">
         <v>46005</v>
       </c>
@@ -1155,7 +1202,7 @@
       <c r="F23" s="1"/>
       <c r="G23" s="4"/>
     </row>
-    <row r="24" spans="2:7" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="13">
         <v>46006</v>
       </c>

--- a/시험공부.xlsx
+++ b/시험공부.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\소프트웨어\GIT\caweb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4240E53-AA60-4492-A5ED-39DE6C79AF55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB8D3E3-5C2D-4FE4-BCD3-4F9D9702C406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{95918DC5-4D7A-419F-A423-84FB36FDBA28}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{95918DC5-4D7A-419F-A423-84FB36FDBA28}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="44">
   <si>
     <t>컴퓨터네트워크</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -66,10 +66,6 @@
   </si>
   <si>
     <t>과제</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14장 복습</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -131,59 +127,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10장 복습</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10장 - 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10장 - 2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11장 - 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11장 복습</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12장 - 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12장 복습</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13장 - 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13장 - 2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13장 복습</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>14장 - 1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>14장 - 2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10 ~ 12주차 과제</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13 ~ 14주차 과제</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -199,6 +147,67 @@
   <si>
     <t>1일차
 BACK와 CONTINUE 버튼 누르면 나오는 화면 구현</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11장 - 1
+(446 ~ 466)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10장 복습
+연습 문제
+자료: 7주차_패키지(Ch10)실습,로또</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11장 복습
+연습문제
+자료: 10주차_오류예외처리(Ch11)실습</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12장 - 1
+(480 ~ 505)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12장 복습
+연습문제
+자료: 11주차_파일입출력(Ch12)실습</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13장 - 1
+(526 ~ 548)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13장 - 2
+(549 ~ 575)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13장 복습
+연습문제
+자료 : 12주차_컬렉션(Ch13)실습</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14장 복습
+연습문제
+자료: 사용자 인터페이스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14주차 e클래스 자료
+15장 -1 ( 668 ~ 690)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15장 연습문제
+10 ~ 12주차 과제
+13 ~ 15주차 과제</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -229,9 +238,32 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-스테이지 1 그림을 그리고 구현하기
-스테이지 표시하기</t>
+</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>과제
+3일차
+스테이지 1 그림을 그리고 구현해보기
+나가기, 스테이지 표시하기
+스테이지 17까지 그림 그리기
+LOADING, SETTING 구현하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4일차
+그린 그림 구현하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10장 - 2
+(398 ~ 429)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10장 - 1
+(386 ~ 397)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -475,7 +507,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -548,7 +580,19 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -886,17 +930,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C2B3A43-413E-47F0-85C4-7C095AF5A1E1}">
   <dimension ref="B1:G24"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.25" customWidth="1"/>
+    <col min="1" max="1" width="2.19921875" customWidth="1"/>
     <col min="2" max="2" width="20.5" customWidth="1"/>
-    <col min="3" max="5" width="19.125" customWidth="1"/>
+    <col min="3" max="3" width="19.09765625" customWidth="1"/>
+    <col min="4" max="4" width="35.5" customWidth="1"/>
+    <col min="5" max="5" width="19.09765625" customWidth="1"/>
     <col min="6" max="6" width="55" customWidth="1"/>
-    <col min="7" max="7" width="19.125" customWidth="1"/>
+    <col min="7" max="7" width="19.09765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="7.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:7" ht="7.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="2" spans="2:7" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B2" s="9"/>
       <c r="C2" s="7" t="s">
         <v>0</v>
@@ -914,21 +960,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:7" ht="59.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7" ht="59.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="12">
         <v>45985</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F3" s="17" t="s">
         <v>7</v>
       </c>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B4" s="10">
         <v>45986</v>
       </c>
@@ -937,7 +983,7 @@
       <c r="E4" s="1"/>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B5" s="10">
         <v>45987</v>
       </c>
@@ -946,185 +992,187 @@
       <c r="E5" s="1"/>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B6" s="10">
         <v>45988</v>
       </c>
       <c r="C6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="22" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B7" s="10">
         <v>45989</v>
       </c>
       <c r="C7" s="1"/>
       <c r="E7" s="23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="B8" s="10">
         <v>45990</v>
       </c>
       <c r="C8" s="1"/>
-      <c r="D8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="24" t="s">
-        <v>41</v>
+      <c r="D8" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="27" t="s">
+        <v>39</v>
       </c>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:7" ht="105" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B9" s="11">
         <v>45991</v>
       </c>
       <c r="C9" s="1"/>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
       <c r="B10" s="12">
         <v>45992</v>
       </c>
       <c r="C10" s="19"/>
-      <c r="D10" s="2" t="s">
-        <v>23</v>
+      <c r="D10" s="25" t="s">
+        <v>29</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="2"/>
+        <v>13</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>41</v>
+      </c>
       <c r="G10" s="3"/>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B11" s="10">
         <v>45993</v>
       </c>
       <c r="C11" s="20"/>
-      <c r="D11" s="1" t="s">
-        <v>26</v>
+      <c r="D11" s="24" t="s">
+        <v>28</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
       <c r="B12" s="10">
         <v>45994</v>
       </c>
       <c r="C12" s="20"/>
-      <c r="D12" s="1" t="s">
-        <v>27</v>
+      <c r="D12" s="24" t="s">
+        <v>30</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="4"/>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B13" s="10">
         <v>45995</v>
       </c>
       <c r="C13" s="20"/>
-      <c r="D13" s="1" t="s">
-        <v>28</v>
+      <c r="D13" s="24" t="s">
+        <v>31</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
       <c r="B14" s="10">
         <v>45996</v>
       </c>
       <c r="C14" s="20"/>
-      <c r="D14" s="1" t="s">
-        <v>29</v>
+      <c r="D14" s="24" t="s">
+        <v>32</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="4"/>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B15" s="10">
         <v>45997</v>
       </c>
       <c r="C15" s="20"/>
-      <c r="D15" s="1" t="s">
-        <v>30</v>
+      <c r="D15" s="24" t="s">
+        <v>33</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="4"/>
     </row>
-    <row r="16" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:7" ht="35.4" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B16" s="11">
         <v>45998</v>
       </c>
       <c r="C16" s="21"/>
-      <c r="D16" s="5" t="s">
-        <v>31</v>
+      <c r="D16" s="26" t="s">
+        <v>34</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="6"/>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
       <c r="B17" s="10">
         <v>45999</v>
       </c>
       <c r="C17" s="1"/>
-      <c r="D17" s="1" t="s">
-        <v>32</v>
+      <c r="D17" s="24" t="s">
+        <v>35</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="4"/>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B18" s="10">
         <v>46000</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E18" s="15" t="s">
         <v>5</v>
@@ -1134,25 +1182,25 @@
       </c>
       <c r="G18" s="4"/>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B19" s="10">
         <v>46001</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="4"/>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
       <c r="B20" s="10">
         <v>46002</v>
       </c>
       <c r="C20" s="1"/>
-      <c r="D20" s="1" t="s">
-        <v>8</v>
+      <c r="D20" s="24" t="s">
+        <v>36</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
@@ -1160,49 +1208,49 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B21" s="10">
         <v>46003</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>35</v>
+        <v>16</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>37</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="4"/>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
       <c r="B22" s="10">
         <v>46004</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>36</v>
+        <v>16</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>38</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="4"/>
     </row>
-    <row r="23" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:7" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B23" s="10">
         <v>46005</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="4"/>
     </row>
-    <row r="24" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:7" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B24" s="13">
         <v>46006</v>
       </c>

--- a/시험공부.xlsx
+++ b/시험공부.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\소프트웨어\GIT\caweb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB8D3E3-5C2D-4FE4-BCD3-4F9D9702C406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E473D509-A6E7-470E-956E-03E4C30E9286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{95918DC5-4D7A-419F-A423-84FB36FDBA28}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="45">
   <si>
     <t>컴퓨터네트워크</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -94,10 +94,6 @@
   </si>
   <si>
     <t>7장 - 복습</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8장 - 1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -111,18 +107,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>9장 - 2 및 복습</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8장 복습</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>9장 - 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>범위 내 복습</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -137,9 +121,6 @@
   <si>
     <t>계획 변경</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5장 SQL</t>
   </si>
   <si>
     <t>6장 SQL</t>
@@ -152,12 +133,6 @@
   <si>
     <t>11장 - 1
 (446 ~ 466)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10장 복습
-연습 문제
-자료: 7주차_패키지(Ch10)실습,로또</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -243,27 +218,61 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>10장 - 1
+(386 ~ 397)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5장 연습문제 - 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5장 SQL
+5장 연습 문제 - 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8장 - 1 후 복습</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9장 - 1 후 복습</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9장 - 2 후 복습</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>복습</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[학교]
+10장 - 2 (398 ~ 429)
+[집]
+10장 복습
+연습 문제
+자료: 7주차_패키지(Ch10)실습,로또</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>과제
-3일차
+[3일차]
 스테이지 1 그림을 그리고 구현해보기
 나가기, 스테이지 표시하기
+LOADING, SETTING 구현하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4일차
 스테이지 17까지 그림 그리기
-LOADING, SETTING 구현하기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4일차
-그린 그림 구현하기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10장 - 2
-(398 ~ 429)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10장 - 1
-(386 ~ 397)</t>
+SETTING, LOADING 구현</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5일차
+플레이어와 적, 그리고 출발지점과 도착지점</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -592,7 +601,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -967,7 +976,7 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F3" s="17" t="s">
         <v>7</v>
@@ -999,7 +1008,7 @@
       <c r="C6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="22" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G6" s="4"/>
     </row>
@@ -1012,7 +1021,7 @@
         <v>11</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G7" s="4"/>
     </row>
@@ -1022,64 +1031,66 @@
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="27" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E8" s="23" t="s">
         <v>10</v>
       </c>
       <c r="F8" s="27" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="2:7" ht="105" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:7" ht="35.4" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B9" s="11">
         <v>45991</v>
       </c>
       <c r="C9" s="1"/>
-      <c r="D9" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="D9" s="24"/>
+      <c r="E9" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="F9" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" s="28" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" ht="121.8" x14ac:dyDescent="0.4">
       <c r="B10" s="12">
         <v>45992</v>
       </c>
       <c r="C10" s="19"/>
       <c r="D10" s="25" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="G10" s="3"/>
-    </row>
-    <row r="11" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
+        <v>42</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
       <c r="B11" s="10">
         <v>45993</v>
       </c>
       <c r="C11" s="20"/>
       <c r="D11" s="24" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="1"/>
+      <c r="F11" s="24" t="s">
+        <v>43</v>
+      </c>
       <c r="G11" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
@@ -1088,12 +1099,14 @@
       </c>
       <c r="C12" s="20"/>
       <c r="D12" s="24" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="1"/>
+        <v>37</v>
+      </c>
+      <c r="F12" s="24" t="s">
+        <v>44</v>
+      </c>
       <c r="G12" s="4"/>
     </row>
     <row r="13" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
@@ -1102,10 +1115,10 @@
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="24" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="4" t="s">
@@ -1118,10 +1131,10 @@
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="24" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="4"/>
@@ -1132,10 +1145,10 @@
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="24" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="4"/>
@@ -1146,10 +1159,10 @@
       </c>
       <c r="C16" s="21"/>
       <c r="D16" s="26" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="6"/>
@@ -1160,7 +1173,7 @@
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="24" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
@@ -1172,7 +1185,7 @@
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E18" s="15" t="s">
         <v>5</v>
@@ -1188,7 +1201,7 @@
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
@@ -1200,7 +1213,7 @@
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="24" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
@@ -1213,10 +1226,10 @@
         <v>46003</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
@@ -1227,10 +1240,10 @@
         <v>46004</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
@@ -1241,7 +1254,7 @@
         <v>46005</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>8</v>

--- a/시험공부.xlsx
+++ b/시험공부.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\소프트웨어\GIT\caweb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E473D509-A6E7-470E-956E-03E4C30E9286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CED61AA-C9D5-4440-B665-D90D76425924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{95918DC5-4D7A-419F-A423-84FB36FDBA28}"/>
+    <workbookView xWindow="1356" yWindow="2220" windowWidth="17280" windowHeight="9960" xr2:uid="{95918DC5-4D7A-419F-A423-84FB36FDBA28}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -115,10 +115,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>14장 - 2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>계획 변경</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -166,17 +162,6 @@
     <t>13장 복습
 연습문제
 자료 : 12주차_컬렉션(Ch13)실습</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14장 복습
-연습문제
-자료: 사용자 인터페이스</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14주차 e클래스 자료
-15장 -1 ( 668 ~ 690)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -223,10 +208,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>5장 연습문제 - 2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>5장 SQL
 5장 연습 문제 - 1</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -245,23 +226,6 @@
   </si>
   <si>
     <t>복습</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[학교]
-10장 - 2 (398 ~ 429)
-[집]
-10장 복습
-연습 문제
-자료: 7주차_패키지(Ch10)실습,로또</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>과제
-[3일차]
-스테이지 1 그림을 그리고 구현해보기
-나가기, 스테이지 표시하기
-LOADING, SETTING 구현하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -273,6 +237,108 @@
   <si>
     <t>5일차
 플레이어와 적, 그리고 출발지점과 도착지점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>과제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+[3일차]
+스테이지 1 그림을 그리고 구현해보기
+나가기, 스테이지 표시하기</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[학교]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">10장 - 2 (398 ~ 423)
+자료 : 로또
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+[집]</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+자료: 7주차_패키지(Ch10)실습
+10장 - 3 (424 ~ 429)
+10장 복습
+연습 문제</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14장 - 2
+7장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14장 복습
+연습문제
+자료: 사용자 인터페이스
+8장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14주차 e클래스 자료
+15장 -1 ( 668 ~ 690)
+9장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+5장 연습문제 - 2
+44번까지만</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -516,7 +582,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -592,9 +658,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -602,6 +665,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1008,7 +1080,7 @@
       <c r="C6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G6" s="4"/>
     </row>
@@ -1021,7 +1093,7 @@
         <v>11</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G7" s="4"/>
     </row>
@@ -1030,14 +1102,14 @@
         <v>45990</v>
       </c>
       <c r="C8" s="1"/>
-      <c r="D8" s="27" t="s">
-        <v>34</v>
+      <c r="D8" s="26" t="s">
+        <v>31</v>
       </c>
       <c r="E8" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="27" t="s">
-        <v>33</v>
+      <c r="F8" s="26" t="s">
+        <v>30</v>
       </c>
       <c r="G8" s="4"/>
     </row>
@@ -1050,29 +1122,29 @@
       <c r="E9" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="27" t="s">
+      <c r="F9" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="28" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="G9" s="27" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" ht="156.6" x14ac:dyDescent="0.4">
       <c r="B10" s="12">
         <v>45992</v>
       </c>
       <c r="C10" s="19"/>
-      <c r="D10" s="25" t="s">
-        <v>41</v>
+      <c r="D10" s="29" t="s">
+        <v>40</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>35</v>
+      <c r="F10" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="30" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
@@ -1081,16 +1153,16 @@
       </c>
       <c r="C11" s="20"/>
       <c r="D11" s="24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F11" s="24" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
@@ -1099,13 +1171,13 @@
       </c>
       <c r="C12" s="20"/>
       <c r="D12" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="G12" s="4"/>
     </row>
@@ -1115,10 +1187,10 @@
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="4" t="s">
@@ -1131,10 +1203,10 @@
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="4"/>
@@ -1145,10 +1217,10 @@
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="4"/>
@@ -1158,8 +1230,8 @@
         <v>45998</v>
       </c>
       <c r="C16" s="21"/>
-      <c r="D16" s="26" t="s">
-        <v>28</v>
+      <c r="D16" s="25" t="s">
+        <v>27</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>17</v>
@@ -1173,7 +1245,7 @@
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
@@ -1195,25 +1267,25 @@
       </c>
       <c r="G18" s="4"/>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B19" s="10">
         <v>46001</v>
       </c>
       <c r="C19" s="1"/>
-      <c r="D19" s="1" t="s">
-        <v>19</v>
+      <c r="D19" s="24" t="s">
+        <v>41</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="4"/>
     </row>
-    <row r="20" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:7" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="B20" s="10">
         <v>46002</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="24" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
@@ -1221,7 +1293,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
       <c r="B21" s="10">
         <v>46003</v>
       </c>
@@ -1229,7 +1301,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
@@ -1243,7 +1315,7 @@
         <v>15</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>

--- a/시험공부.xlsx
+++ b/시험공부.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\소프트웨어\GIT\caweb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CED61AA-C9D5-4440-B665-D90D76425924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{884A4986-410C-410C-B654-406B69295FB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1356" yWindow="2220" windowWidth="17280" windowHeight="9960" xr2:uid="{95918DC5-4D7A-419F-A423-84FB36FDBA28}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{95918DC5-4D7A-419F-A423-84FB36FDBA28}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -237,35 +237,6 @@
   <si>
     <t>5일차
 플레이어와 적, 그리고 출발지점과 도착지점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>과제</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-[3일차]
-스테이지 1 그림을 그리고 구현해보기
-나가기, 스테이지 표시하기</t>
-    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -339,6 +310,12 @@
     <t xml:space="preserve">
 5장 연습문제 - 2
 44번까지만</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>과제
+[3일차]
+어떻게 하는지 알아보기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -582,7 +559,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -667,14 +644,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1134,17 +1114,17 @@
         <v>45992</v>
       </c>
       <c r="C10" s="19"/>
-      <c r="D10" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="D10" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="G10" s="30" t="s">
+      <c r="F10" s="18" t="s">
         <v>44</v>
+      </c>
+      <c r="G10" s="29" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
@@ -1155,7 +1135,7 @@
       <c r="D11" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="31" t="s">
         <v>14</v>
       </c>
       <c r="F11" s="24" t="s">
@@ -1273,7 +1253,7 @@
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
@@ -1285,7 +1265,7 @@
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
@@ -1301,7 +1281,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>

--- a/시험공부.xlsx
+++ b/시험공부.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\소프트웨어\GIT\caweb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{884A4986-410C-410C-B654-406B69295FB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A2DC037-C5EE-440B-9709-8B0A265BB5C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{95918DC5-4D7A-419F-A423-84FB36FDBA28}"/>
   </bookViews>
@@ -226,17 +226,6 @@
   </si>
   <si>
     <t>복습</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4일차
-스테이지 17까지 그림 그리기
-SETTING, LOADING 구현</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5일차
-플레이어와 적, 그리고 출발지점과 도착지점</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -316,6 +305,17 @@
     <t>과제
 [3일차]
 어떻게 하는지 알아보기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5일차
+플레이어와 적 그림 그리기
+스테이지 적용하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4일차
+스테이지 10까지 그림 그리기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1115,19 +1115,19 @@
       </c>
       <c r="C10" s="19"/>
       <c r="D10" s="28" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E10" s="30" t="s">
         <v>13</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B11" s="10">
         <v>45993</v>
       </c>
@@ -1138,8 +1138,8 @@
       <c r="E11" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="24" t="s">
-        <v>37</v>
+      <c r="F11" s="26" t="s">
+        <v>44</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>20</v>
@@ -1157,7 +1157,7 @@
         <v>33</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G12" s="4"/>
     </row>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="24" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="24" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
@@ -1281,7 +1281,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>

--- a/시험공부.xlsx
+++ b/시험공부.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\소프트웨어\GIT\caweb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A2DC037-C5EE-440B-9709-8B0A265BB5C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CF75C35-1322-4BC2-8E1E-1ED41016ECA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{95918DC5-4D7A-419F-A423-84FB36FDBA28}"/>
+    <workbookView xWindow="3648" yWindow="1836" windowWidth="17280" windowHeight="9960" xr2:uid="{95918DC5-4D7A-419F-A423-84FB36FDBA28}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -117,9 +117,6 @@
   <si>
     <t>계획 변경</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6장 SQL</t>
   </si>
   <si>
     <t>1일차
@@ -316,6 +313,10 @@
   <si>
     <t>4일차
 스테이지 10까지 그림 그리기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6장 SQL</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1073,7 +1074,7 @@
         <v>11</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G7" s="4"/>
     </row>
@@ -1083,13 +1084,13 @@
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E8" s="23" t="s">
         <v>10</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G8" s="4"/>
     </row>
@@ -1106,7 +1107,7 @@
         <v>7</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="2:7" ht="156.6" x14ac:dyDescent="0.4">
@@ -1115,16 +1116,16 @@
       </c>
       <c r="C10" s="19"/>
       <c r="D10" s="28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E10" s="30" t="s">
         <v>13</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
@@ -1132,18 +1133,16 @@
         <v>45993</v>
       </c>
       <c r="C11" s="20"/>
-      <c r="D11" s="24" t="s">
-        <v>22</v>
+      <c r="D11" s="26" t="s">
+        <v>21</v>
       </c>
       <c r="E11" s="31" t="s">
         <v>14</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>20</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="G11" s="4"/>
     </row>
     <row r="12" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
       <c r="B12" s="10">
@@ -1151,15 +1150,17 @@
       </c>
       <c r="C12" s="20"/>
       <c r="D12" s="24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="G12" s="4"/>
+        <v>42</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="13" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B13" s="10">
@@ -1167,10 +1168,10 @@
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="4" t="s">
@@ -1183,10 +1184,10 @@
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="4"/>
@@ -1197,10 +1198,10 @@
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="4"/>
@@ -1211,7 +1212,7 @@
       </c>
       <c r="C16" s="21"/>
       <c r="D16" s="25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>17</v>
@@ -1225,7 +1226,7 @@
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
@@ -1253,7 +1254,7 @@
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
@@ -1265,7 +1266,7 @@
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
@@ -1281,7 +1282,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
@@ -1295,7 +1296,7 @@
         <v>15</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>

--- a/시험공부.xlsx
+++ b/시험공부.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\소프트웨어\GIT\caweb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CF75C35-1322-4BC2-8E1E-1ED41016ECA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F6AD8DB-A024-466E-B972-ECB36F0F3AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3648" yWindow="1836" windowWidth="17280" windowHeight="9960" xr2:uid="{95918DC5-4D7A-419F-A423-84FB36FDBA28}"/>
+    <workbookView xWindow="4590" yWindow="2955" windowWidth="16005" windowHeight="12525" xr2:uid="{95918DC5-4D7A-419F-A423-84FB36FDBA28}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="48">
   <si>
     <t>컴퓨터네트워크</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -70,10 +70,6 @@
   </si>
   <si>
     <t>전범위 복습</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7장 SQL</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -126,12 +122,6 @@
   <si>
     <t>11장 - 1
 (446 ~ 466)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11장 복습
-연습문제
-자료: 10주차_오류예외처리(Ch11)실습</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -305,18 +295,40 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>4일차
+스테이지 10까지 그림 그리기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6장 SQL - 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7장 SQL - 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7장 SQL - 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6장 SQL - 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11장 복습
+연습문제
+자료: 10주차_오류예외처리(Ch11)실습</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연습문제 다 보기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>5일차
 플레이어와 적 그림 그리기
-스테이지 적용하기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4일차
-스테이지 10까지 그림 그리기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6장 SQL</t>
+1~2스테이지 적용하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -560,7 +572,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -655,6 +667,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -992,19 +1007,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C2B3A43-413E-47F0-85C4-7C095AF5A1E1}">
   <dimension ref="B1:G24"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.19921875" customWidth="1"/>
+    <col min="1" max="1" width="2.25" customWidth="1"/>
     <col min="2" max="2" width="20.5" customWidth="1"/>
-    <col min="3" max="3" width="19.09765625" customWidth="1"/>
+    <col min="3" max="3" width="19.125" customWidth="1"/>
     <col min="4" max="4" width="35.5" customWidth="1"/>
-    <col min="5" max="5" width="19.09765625" customWidth="1"/>
+    <col min="5" max="5" width="19.125" customWidth="1"/>
     <col min="6" max="6" width="55" customWidth="1"/>
-    <col min="7" max="7" width="19.09765625" customWidth="1"/>
+    <col min="7" max="7" width="19.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="7.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="2" spans="2:7" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:7" ht="7.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="9"/>
       <c r="C2" s="7" t="s">
         <v>0</v>
@@ -1022,21 +1037,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:7" ht="59.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:7" ht="59.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="12">
         <v>45985</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F3" s="17" t="s">
         <v>7</v>
       </c>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B4" s="10">
         <v>45986</v>
       </c>
@@ -1045,7 +1060,7 @@
       <c r="E4" s="1"/>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B5" s="10">
         <v>45987</v>
       </c>
@@ -1054,191 +1069,195 @@
       <c r="E5" s="1"/>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B6" s="10">
         <v>45988</v>
       </c>
       <c r="C6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B7" s="10">
         <v>45989</v>
       </c>
       <c r="C7" s="1"/>
       <c r="E7" s="23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="2:7" ht="69.599999999999994" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:7" ht="66" x14ac:dyDescent="0.3">
       <c r="B8" s="10">
         <v>45990</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="26" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="2:7" ht="35.4" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="11">
         <v>45991</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="24"/>
       <c r="E9" s="23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F9" s="26" t="s">
         <v>7</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" ht="156.6" x14ac:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" ht="148.5" x14ac:dyDescent="0.3">
       <c r="B10" s="12">
         <v>45992</v>
       </c>
       <c r="C10" s="19"/>
       <c r="D10" s="28" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E10" s="30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B11" s="10">
         <v>45993</v>
       </c>
       <c r="C11" s="20"/>
       <c r="D11" s="26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G11" s="4"/>
     </row>
-    <row r="12" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B12" s="10">
         <v>45994</v>
       </c>
       <c r="C12" s="20"/>
-      <c r="D12" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="D12" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="G12" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B13" s="10">
         <v>45995</v>
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="24" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B14" s="10">
         <v>45996</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="24" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F14" s="1"/>
-      <c r="G14" s="4"/>
-    </row>
-    <row r="15" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="G14" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B15" s="10">
         <v>45997</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="24" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F15" s="1"/>
-      <c r="G15" s="4"/>
-    </row>
-    <row r="16" spans="2:7" ht="35.4" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="G15" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="11">
         <v>45998</v>
       </c>
       <c r="C16" s="21"/>
       <c r="D16" s="25" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="6"/>
     </row>
-    <row r="17" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B17" s="10">
         <v>45999</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="24" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="4"/>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" s="10">
         <v>46000</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E18" s="15" t="s">
         <v>5</v>
@@ -1248,25 +1267,27 @@
       </c>
       <c r="G18" s="4"/>
     </row>
-    <row r="19" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B19" s="10">
         <v>46001</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="24" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
-      <c r="G19" s="4"/>
-    </row>
-    <row r="20" spans="2:7" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="G19" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" ht="66" x14ac:dyDescent="0.3">
       <c r="B20" s="10">
         <v>46002</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="24" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
@@ -1274,40 +1295,40 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B21" s="10">
         <v>46003</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="4"/>
     </row>
-    <row r="22" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B22" s="10">
         <v>46004</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="4"/>
     </row>
-    <row r="23" spans="2:7" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="10">
         <v>46005</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>8</v>
@@ -1316,7 +1337,7 @@
       <c r="F23" s="1"/>
       <c r="G23" s="4"/>
     </row>
-    <row r="24" spans="2:7" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="13">
         <v>46006</v>
       </c>

--- a/시험공부.xlsx
+++ b/시험공부.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\소프트웨어\GIT\caweb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F6AD8DB-A024-466E-B972-ECB36F0F3AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D5AEBA-BCB8-48C1-ACA9-D696D059F799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4590" yWindow="2955" windowWidth="16005" windowHeight="12525" xr2:uid="{95918DC5-4D7A-419F-A423-84FB36FDBA28}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{95918DC5-4D7A-419F-A423-84FB36FDBA28}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -328,7 +328,7 @@
   <si>
     <t>5일차
 플레이어와 적 그림 그리기
-1~2스테이지 적용하기</t>
+1스테이지 적용하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1007,19 +1007,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C2B3A43-413E-47F0-85C4-7C095AF5A1E1}">
   <dimension ref="B1:G24"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.25" customWidth="1"/>
+    <col min="1" max="1" width="2.19921875" customWidth="1"/>
     <col min="2" max="2" width="20.5" customWidth="1"/>
-    <col min="3" max="3" width="19.125" customWidth="1"/>
+    <col min="3" max="3" width="19.09765625" customWidth="1"/>
     <col min="4" max="4" width="35.5" customWidth="1"/>
-    <col min="5" max="5" width="19.125" customWidth="1"/>
+    <col min="5" max="5" width="19.09765625" customWidth="1"/>
     <col min="6" max="6" width="55" customWidth="1"/>
-    <col min="7" max="7" width="19.125" customWidth="1"/>
+    <col min="7" max="7" width="19.09765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="7.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:7" ht="7.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="2" spans="2:7" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B2" s="9"/>
       <c r="C2" s="7" t="s">
         <v>0</v>
@@ -1037,7 +1037,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:7" ht="59.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7" ht="59.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="12">
         <v>45985</v>
       </c>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B4" s="10">
         <v>45986</v>
       </c>
@@ -1060,7 +1060,7 @@
       <c r="E4" s="1"/>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B5" s="10">
         <v>45987</v>
       </c>
@@ -1069,7 +1069,7 @@
       <c r="E5" s="1"/>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B6" s="10">
         <v>45988</v>
       </c>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B7" s="10">
         <v>45989</v>
       </c>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="2:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="B8" s="10">
         <v>45990</v>
       </c>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:7" ht="35.4" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B9" s="11">
         <v>45991</v>
       </c>
@@ -1125,7 +1125,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="2:7" ht="148.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:7" ht="156.6" x14ac:dyDescent="0.4">
       <c r="B10" s="12">
         <v>45992</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B11" s="10">
         <v>45993</v>
       </c>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="G11" s="4"/>
     </row>
-    <row r="12" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
       <c r="B12" s="10">
         <v>45994</v>
       </c>
@@ -1177,12 +1177,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B13" s="10">
         <v>45995</v>
       </c>
       <c r="C13" s="20"/>
-      <c r="D13" s="24" t="s">
+      <c r="D13" s="26" t="s">
         <v>21</v>
       </c>
       <c r="E13" s="1" t="s">
@@ -1193,7 +1193,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
       <c r="B14" s="10">
         <v>45996</v>
       </c>
@@ -1209,7 +1209,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B15" s="10">
         <v>45997</v>
       </c>
@@ -1225,7 +1225,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:7" ht="35.4" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B16" s="11">
         <v>45998</v>
       </c>
@@ -1239,7 +1239,7 @@
       <c r="F16" s="5"/>
       <c r="G16" s="6"/>
     </row>
-    <row r="17" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
       <c r="B17" s="10">
         <v>45999</v>
       </c>
@@ -1251,7 +1251,7 @@
       <c r="F17" s="1"/>
       <c r="G17" s="4"/>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B18" s="10">
         <v>46000</v>
       </c>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="G18" s="4"/>
     </row>
-    <row r="19" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B19" s="10">
         <v>46001</v>
       </c>
@@ -1281,7 +1281,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="2:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:7" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="B20" s="10">
         <v>46002</v>
       </c>
@@ -1295,7 +1295,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
       <c r="B21" s="10">
         <v>46003</v>
       </c>
@@ -1309,7 +1309,7 @@
       <c r="F21" s="1"/>
       <c r="G21" s="4"/>
     </row>
-    <row r="22" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
       <c r="B22" s="10">
         <v>46004</v>
       </c>
@@ -1323,7 +1323,7 @@
       <c r="F22" s="1"/>
       <c r="G22" s="4"/>
     </row>
-    <row r="23" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:7" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B23" s="10">
         <v>46005</v>
       </c>
@@ -1337,7 +1337,7 @@
       <c r="F23" s="1"/>
       <c r="G23" s="4"/>
     </row>
-    <row r="24" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:7" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B24" s="13">
         <v>46006</v>
       </c>
@@ -1354,5 +1354,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/시험공부.xlsx
+++ b/시험공부.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\소프트웨어\GIT\caweb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D5AEBA-BCB8-48C1-ACA9-D696D059F799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21022C06-E6BA-4FBF-8FCA-F7E908401DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{95918DC5-4D7A-419F-A423-84FB36FDBA28}"/>
+    <workbookView xWindow="4236" yWindow="2328" windowWidth="17280" windowHeight="9960" xr2:uid="{95918DC5-4D7A-419F-A423-84FB36FDBA28}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="47">
   <si>
     <t>컴퓨터네트워크</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -201,14 +201,6 @@
   </si>
   <si>
     <t>8장 - 1 후 복습</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>9장 - 1 후 복습</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>9장 - 2 후 복습</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -304,18 +296,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>7장 SQL - 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7장 SQL - 2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6장 SQL - 2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>11장 복습
 연습문제
 자료: 10주차_오류예외처리(Ch11)실습</t>
@@ -329,6 +309,28 @@
     <t>5일차
 플레이어와 적 그림 그리기
 1스테이지 적용하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7일차
+2~5스테이지 적용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9장 - 2, tar ~ 
+복습</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9장 - 1, ~dnf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6일차
+1스테이지 플레이할 수 있도록 적용해보기
+2스테이지와 연결하기
+----------------
+1일차 - 블록게임</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1131,16 +1133,16 @@
       </c>
       <c r="C10" s="19"/>
       <c r="D10" s="28" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E10" s="30" t="s">
         <v>12</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
@@ -1155,7 +1157,7 @@
         <v>13</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G11" s="4"/>
     </row>
@@ -1165,16 +1167,16 @@
       </c>
       <c r="C12" s="20"/>
       <c r="D12" s="22" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E12" s="23" t="s">
         <v>30</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G12" s="32" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
@@ -1185,29 +1187,27 @@
       <c r="D13" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F13" s="1"/>
-      <c r="G13" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="E13" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="24"/>
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="2:7" ht="87" x14ac:dyDescent="0.4">
       <c r="B14" s="10">
         <v>45996</v>
       </c>
       <c r="C14" s="20"/>
-      <c r="D14" s="24" t="s">
+      <c r="D14" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F14" s="1"/>
-      <c r="G14" s="4" t="s">
-        <v>42</v>
-      </c>
+      <c r="E14" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14" s="4"/>
     </row>
     <row r="15" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B15" s="10">
@@ -1218,12 +1218,12 @@
         <v>23</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F15" s="1"/>
-      <c r="G15" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="24" t="s">
         <v>43</v>
       </c>
+      <c r="G15" s="4"/>
     </row>
     <row r="16" spans="2:7" ht="35.4" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B16" s="11">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="24" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="2:7" ht="69.599999999999994" x14ac:dyDescent="0.4">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="24" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
@@ -1303,7 +1303,7 @@
         <v>14</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>

--- a/시험공부.xlsx
+++ b/시험공부.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\소프트웨어\GIT\caweb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21022C06-E6BA-4FBF-8FCA-F7E908401DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF7C8BE7-703B-4C0D-AB1E-239F71F3C47A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4236" yWindow="2328" windowWidth="17280" windowHeight="9960" xr2:uid="{95918DC5-4D7A-419F-A423-84FB36FDBA28}"/>
+    <workbookView xWindow="1650" yWindow="855" windowWidth="22590" windowHeight="14835" xr2:uid="{95918DC5-4D7A-419F-A423-84FB36FDBA28}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="45">
   <si>
     <t>컴퓨터네트워크</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -66,10 +66,6 @@
   </si>
   <si>
     <t>과제</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>전범위 복습</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -103,14 +99,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>범위 내 복습</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14장 - 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>계획 변경</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -149,12 +137,6 @@
     <t>13장 복습
 연습문제
 자료 : 12주차_컬렉션(Ch13)실습</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15장 연습문제
-10 ~ 12주차 과제
-13 ~ 15주차 과제</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -201,10 +183,6 @@
   </si>
   <si>
     <t>8장 - 1 후 복습</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>복습</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -262,76 +240,90 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t xml:space="preserve">
+5장 연습문제 - 2
+44번까지만</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>과제
+[3일차]
+어떻게 하는지 알아보기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4일차
+스테이지 10까지 그림 그리기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6장 SQL - 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11장 복습
+연습문제
+자료: 10주차_오류예외처리(Ch11)실습</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연습문제 다 보기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5일차
+플레이어와 적 그림 그리기
+1스테이지 적용하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9장 - 2, tar ~ 
+복습</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9장 - 1, ~dnf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>복습 (6 ~ 9장)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>복습 (1 ~ 5장)
+2, 3장 제외</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테이지 3까지 적용
+(그라운드 영역 제한 제외)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테이지 4 ~ 10까지 적용
+그라운드 영역 추가
+코인 추가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15장 연습문제
+10 ~ 12주차 과제
+13 ~ 15주차 과제
+9장
+전범위 복습</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>14장 복습
 연습문제
 자료: 사용자 인터페이스
+14주차 e클래스 자료
+15장 -1 ( 668 ~ 690)
 8장</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>14주차 e클래스 자료
-15장 -1 ( 668 ~ 690)
-9장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">
-5장 연습문제 - 2
-44번까지만</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>과제
-[3일차]
-어떻게 하는지 알아보기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4일차
-스테이지 10까지 그림 그리기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6장 SQL - 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11장 복습
-연습문제
-자료: 10주차_오류예외처리(Ch11)실습</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>연습문제 다 보기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5일차
-플레이어와 적 그림 그리기
-1스테이지 적용하기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7일차
-2~5스테이지 적용</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>9장 - 2, tar ~ 
-복습</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>9장 - 1, ~dnf</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6일차
-1스테이지 플레이할 수 있도록 적용해보기
-2스테이지와 연결하기
-----------------
-1일차 - 블록게임</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>14장 - 1</t>
   </si>
 </sst>
 </file>
@@ -590,9 +582,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -673,6 +662,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1009,52 +1001,52 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C2B3A43-413E-47F0-85C4-7C095AF5A1E1}">
   <dimension ref="B1:G24"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.19921875" customWidth="1"/>
+    <col min="1" max="1" width="2.25" customWidth="1"/>
     <col min="2" max="2" width="20.5" customWidth="1"/>
-    <col min="3" max="3" width="19.09765625" customWidth="1"/>
+    <col min="3" max="3" width="19.125" customWidth="1"/>
     <col min="4" max="4" width="35.5" customWidth="1"/>
-    <col min="5" max="5" width="19.09765625" customWidth="1"/>
+    <col min="5" max="5" width="19.125" customWidth="1"/>
     <col min="6" max="6" width="55" customWidth="1"/>
-    <col min="7" max="7" width="19.09765625" customWidth="1"/>
+    <col min="7" max="7" width="19.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="7.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="2" spans="2:7" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="9"/>
-      <c r="C2" s="7" t="s">
+    <row r="1" spans="2:7" ht="7.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="8"/>
+      <c r="C2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:7" ht="59.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="12">
+    <row r="3" spans="2:7" ht="59.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="11">
         <v>45985</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
-      <c r="E3" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="17" t="s">
+      <c r="E3" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="16" t="s">
         <v>7</v>
       </c>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="B4" s="10">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="9">
         <v>45986</v>
       </c>
       <c r="C4" s="1"/>
@@ -1062,8 +1054,8 @@
       <c r="E4" s="1"/>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="B5" s="10">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="9">
         <v>45987</v>
       </c>
       <c r="C5" s="1"/>
@@ -1071,285 +1063,283 @@
       <c r="E5" s="1"/>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="B6" s="10">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="9">
         <v>45988</v>
       </c>
       <c r="C6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="22" t="s">
+      <c r="F6" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="4"/>
+    </row>
+    <row r="7" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B7" s="9">
+        <v>45989</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="E7" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="4"/>
+    </row>
+    <row r="8" spans="2:7" ht="66" x14ac:dyDescent="0.3">
+      <c r="B8" s="9">
+        <v>45990</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="10">
+        <v>45991</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" s="26" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" ht="148.5" x14ac:dyDescent="0.3">
+      <c r="B10" s="11">
+        <v>45992</v>
+      </c>
+      <c r="C10" s="18"/>
+      <c r="D10" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" s="28" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B11" s="9">
+        <v>45993</v>
+      </c>
+      <c r="C11" s="19"/>
+      <c r="D11" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B12" s="9">
+        <v>45994</v>
+      </c>
+      <c r="C12" s="19"/>
+      <c r="D12" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="31" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B13" s="9">
+        <v>45995</v>
+      </c>
+      <c r="C13" s="19"/>
+      <c r="D13" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="4"/>
-    </row>
-    <row r="7" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B7" s="10">
-        <v>45989</v>
-      </c>
-      <c r="C7" s="1"/>
-      <c r="E7" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="22" t="s">
+      <c r="E13" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="23"/>
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B14" s="9">
+        <v>45996</v>
+      </c>
+      <c r="C14" s="19"/>
+      <c r="D14" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="G7" s="4"/>
-    </row>
-    <row r="8" spans="2:7" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="B8" s="10">
-        <v>45990</v>
-      </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="4"/>
-    </row>
-    <row r="9" spans="2:7" ht="35.4" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="11">
-        <v>45991</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="G9" s="27" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" ht="156.6" x14ac:dyDescent="0.4">
-      <c r="B10" s="12">
-        <v>45992</v>
-      </c>
-      <c r="C10" s="19"/>
-      <c r="D10" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="G10" s="29" t="s">
+      <c r="E14" s="25" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="11" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B11" s="10">
-        <v>45993</v>
-      </c>
-      <c r="C11" s="20"/>
-      <c r="D11" s="26" t="s">
+      <c r="F14" s="23"/>
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B15" s="9">
+        <v>45997</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="10">
+        <v>45998</v>
+      </c>
+      <c r="C16" s="20"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="F16" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="G16" s="5"/>
+    </row>
+    <row r="17" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B17" s="9">
+        <v>45999</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="26" t="s">
+      <c r="E17" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G11" s="4"/>
-    </row>
-    <row r="12" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
-      <c r="B12" s="10">
-        <v>45994</v>
-      </c>
-      <c r="C12" s="20"/>
-      <c r="D12" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="G12" s="32" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B13" s="10">
-        <v>45995</v>
-      </c>
-      <c r="C13" s="20"/>
-      <c r="D13" s="26" t="s">
+      <c r="F17" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="G17" s="4"/>
+    </row>
+    <row r="18" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B18" s="9">
+        <v>46000</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="F13" s="24"/>
-      <c r="G13" s="4"/>
-    </row>
-    <row r="14" spans="2:7" ht="87" x14ac:dyDescent="0.4">
-      <c r="B14" s="10">
-        <v>45996</v>
-      </c>
-      <c r="C14" s="20"/>
-      <c r="D14" s="26" t="s">
+      <c r="E18" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B19" s="9">
+        <v>46001</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="23" t="s">
         <v>22</v>
-      </c>
-      <c r="E14" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="F14" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="G14" s="4"/>
-    </row>
-    <row r="15" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B15" s="10">
-        <v>45997</v>
-      </c>
-      <c r="C15" s="20"/>
-      <c r="D15" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F15" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="G15" s="4"/>
-    </row>
-    <row r="16" spans="2:7" ht="35.4" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B16" s="11">
-        <v>45998</v>
-      </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" s="5"/>
-      <c r="G16" s="6"/>
-    </row>
-    <row r="17" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
-      <c r="B17" s="10">
-        <v>45999</v>
-      </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="4"/>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="B18" s="10">
-        <v>46000</v>
-      </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="G18" s="4"/>
-    </row>
-    <row r="19" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B19" s="10">
-        <v>46001</v>
-      </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="24" t="s">
-        <v>33</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="B20" s="10">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B20" s="9">
         <v>46002</v>
       </c>
       <c r="C20" s="1"/>
-      <c r="D20" s="24" t="s">
-        <v>34</v>
+      <c r="D20" s="23" t="s">
+        <v>44</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
-      <c r="G20" s="16" t="s">
+      <c r="G20" s="15" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
-      <c r="B21" s="10">
+    <row r="21" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B21" s="9">
         <v>46003</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21" s="24" t="s">
-        <v>35</v>
+        <v>13</v>
+      </c>
+      <c r="D21" s="23" t="s">
+        <v>28</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="4"/>
     </row>
-    <row r="22" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
-      <c r="B22" s="10">
+    <row r="22" spans="2:7" ht="115.5" x14ac:dyDescent="0.3">
+      <c r="B22" s="9">
         <v>46004</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" s="24" t="s">
-        <v>26</v>
+        <v>13</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>43</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="4"/>
     </row>
-    <row r="23" spans="2:7" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B23" s="10">
+    <row r="23" spans="2:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="9">
         <v>46005</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
+      </c>
+      <c r="D23" s="23" t="s">
+        <v>42</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="4"/>
     </row>
-    <row r="24" spans="2:7" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B24" s="13">
+    <row r="24" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="12">
         <v>46006</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="C24" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="D24" s="14" t="s">
+      <c r="D24" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="8"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/시험공부.xlsx
+++ b/시험공부.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\소프트웨어\GIT\caweb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF7C8BE7-703B-4C0D-AB1E-239F71F3C47A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D2AF533-9C6A-4BAA-BFA8-6B10B65C95FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1650" yWindow="855" windowWidth="22590" windowHeight="14835" xr2:uid="{95918DC5-4D7A-419F-A423-84FB36FDBA28}"/>
+    <workbookView xWindow="4590" yWindow="645" windowWidth="22590" windowHeight="14835" xr2:uid="{95918DC5-4D7A-419F-A423-84FB36FDBA28}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="44">
   <si>
     <t>컴퓨터네트워크</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -126,17 +126,6 @@
   <si>
     <t>13장 - 1
 (526 ~ 548)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13장 - 2
-(549 ~ 575)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13장 복습
-연습문제
-자료 : 12주차_컬렉션(Ch13)실습</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -300,12 +289,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>스테이지 4 ~ 10까지 적용
-그라운드 영역 추가
-코인 추가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>15장 연습문제
 10 ~ 12주차 과제
 13 ~ 15주차 과제
@@ -324,6 +307,42 @@
   </si>
   <si>
     <t>14장 - 1</t>
+  </si>
+  <si>
+    <t>13장 - 2
+(549 ~ 575)
+13장 복습
+연습문제
+자료 : 12주차_컬렉션(Ch13)실습</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>스테이지 4 ~ 7까지 적용</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+그라운드 영역 추가
+버그 수정하기</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -566,7 +585,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -663,7 +682,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1093,13 +1115,13 @@
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="25" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E8" s="22" t="s">
         <v>8</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G8" s="4"/>
     </row>
@@ -1116,7 +1138,7 @@
         <v>7</v>
       </c>
       <c r="G9" s="26" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="2:7" ht="148.5" x14ac:dyDescent="0.3">
@@ -1125,16 +1147,16 @@
       </c>
       <c r="C10" s="18"/>
       <c r="D10" s="27" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E10" s="29" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -1149,7 +1171,7 @@
         <v>12</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G11" s="4"/>
     </row>
@@ -1159,16 +1181,16 @@
       </c>
       <c r="C12" s="19"/>
       <c r="D12" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="E12" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="21" t="s">
-        <v>35</v>
-      </c>
       <c r="G12" s="31" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -1180,7 +1202,7 @@
         <v>18</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F13" s="23"/>
       <c r="G13" s="4"/>
@@ -1194,7 +1216,7 @@
         <v>19</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F14" s="23"/>
       <c r="G14" s="4"/>
@@ -1216,10 +1238,10 @@
       <c r="C16" s="20"/>
       <c r="D16" s="24"/>
       <c r="E16" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="F16" s="32" t="s">
-        <v>40</v>
+        <v>37</v>
+      </c>
+      <c r="F16" s="33" t="s">
+        <v>38</v>
       </c>
       <c r="G16" s="5"/>
     </row>
@@ -1228,14 +1250,12 @@
         <v>45999</v>
       </c>
       <c r="C17" s="1"/>
-      <c r="D17" s="23" t="s">
-        <v>20</v>
-      </c>
+      <c r="D17" s="23"/>
       <c r="E17" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F17" s="23" t="s">
-        <v>41</v>
+        <v>36</v>
+      </c>
+      <c r="F17" s="32" t="s">
+        <v>43</v>
       </c>
       <c r="G17" s="4"/>
     </row>
@@ -1245,7 +1265,7 @@
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E18" s="14" t="s">
         <v>6</v>
@@ -1254,21 +1274,21 @@
         <v>5</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" ht="99" x14ac:dyDescent="0.3">
       <c r="B19" s="9">
         <v>46001</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="23" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.3">
@@ -1277,7 +1297,7 @@
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="23" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
@@ -1293,7 +1313,7 @@
         <v>13</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
@@ -1307,7 +1327,7 @@
         <v>13</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
@@ -1321,7 +1341,7 @@
         <v>13</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>

--- a/시험공부.xlsx
+++ b/시험공부.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\소프트웨어\GIT\caweb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D2AF533-9C6A-4BAA-BFA8-6B10B65C95FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFEC536E-1F0A-421D-9908-9916F7780846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4590" yWindow="645" windowWidth="22590" windowHeight="14835" xr2:uid="{95918DC5-4D7A-419F-A423-84FB36FDBA28}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="45">
   <si>
     <t>컴퓨터네트워크</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -275,10 +275,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>복습 (6 ~ 9장)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>복습 (1 ~ 5장)
 2, 3장 제외</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -317,31 +313,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>스테이지 4 ~ 7까지 적용</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
+    <t>스테이지 4 ~ 7까지 적용
 그라운드 영역 추가
 버그 수정하기</t>
-    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2교시 암기
+시험</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>복습 (6 ~ 9장)
+과제 암기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -682,10 +666,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1238,10 +1222,10 @@
       <c r="C16" s="20"/>
       <c r="D16" s="24"/>
       <c r="E16" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" s="32" t="s">
         <v>37</v>
-      </c>
-      <c r="F16" s="33" t="s">
-        <v>38</v>
       </c>
       <c r="G16" s="5"/>
     </row>
@@ -1251,11 +1235,11 @@
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="23"/>
-      <c r="E17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F17" s="32" t="s">
-        <v>43</v>
+      <c r="E17" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>42</v>
       </c>
       <c r="G17" s="4"/>
     </row>
@@ -1267,8 +1251,8 @@
       <c r="D18" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="14" t="s">
-        <v>6</v>
+      <c r="E18" s="33" t="s">
+        <v>43</v>
       </c>
       <c r="F18" s="14" t="s">
         <v>5</v>
@@ -1283,7 +1267,7 @@
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
@@ -1297,7 +1281,7 @@
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
@@ -1327,7 +1311,7 @@
         <v>13</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
@@ -1341,7 +1325,7 @@
         <v>13</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>

--- a/시험공부.xlsx
+++ b/시험공부.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\소프트웨어\GIT\caweb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{714B68F4-9472-403D-A5C4-E5C8E9EC7294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41BF0FAB-F617-4EEE-B83C-7FD95CBA6F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4236" yWindow="2328" windowWidth="17280" windowHeight="9960" xr2:uid="{95918DC5-4D7A-419F-A423-84FB36FDBA28}"/>
   </bookViews>
@@ -98,10 +98,24 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>7 ~ 9장 복습
+    <r>
+      <t xml:space="preserve">7 ~ 9장 복습
 10 ~ 15장 복습
-15장 실습 / 14장 서버와 클라이언트 복습
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>15장 실습 / 14장 서버와 클라이언트 복습
 과제 복습</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -268,13 +282,13 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -646,7 +660,7 @@
       <c r="B3" s="6">
         <v>46003</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="8" t="s">
@@ -659,7 +673,7 @@
       <c r="B4" s="6">
         <v>46004</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="8" t="s">
@@ -675,7 +689,7 @@
       <c r="C5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="11" t="s">
         <v>12</v>
       </c>
       <c r="F5" s="1"/>
@@ -685,10 +699,10 @@
       <c r="B6" s="7">
         <v>46006</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="10" t="s">
         <v>6</v>
       </c>
       <c r="E6" s="3"/>
